--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
 dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}fhs-2:Can only have estimatedAge if age[x] is present {age.exists() or estimatedAge.empty()}fhs-1:Can have age[x] or born[x], but not both {age.empty() or born.empty()}</t>
   </si>
   <si>
-    <t>Familienanamnese</t>
+    <t>familienanamnese</t>
   </si>
   <si>
     <t>mide-dataelement-1740</t>
@@ -460,7 +460,7 @@
     <t>Extension zur Angabe, ob ein Familienmitglied von der gleichen seltenen Erkrankung betroffen ist wie der Patient</t>
   </si>
   <si>
-    <t>Familienanamnese.GleicheSE</t>
+    <t>familienanamnese.gleicheSE</t>
   </si>
   <si>
     <t>FamilyMemberHistory.modifierExtension</t>
@@ -659,7 +659,7 @@
     <t>http://terminology.hl7.org/ValueSet/v3-FamilyMember</t>
   </si>
   <si>
-    <t>Familienanamnese.Verwandtschaftsverhaeltnis</t>
+    <t>familienanamnese.verwandtschaftsverhaeltnis</t>
   </si>
   <si>
     <t>FamilyMemberHistory.relationship.id</t>
@@ -939,7 +939,7 @@
     <t>http://hl7.org/fhir/ValueSet/administrative-gender</t>
   </si>
   <si>
-    <t>Familienanamnese.Geschlecht</t>
+    <t>familienanamnese.geschlecht</t>
   </si>
   <si>
     <t>FamilyMemberHistory.born[x]</t>
@@ -1026,7 +1026,7 @@
     <t>deceasedBoolean</t>
   </si>
   <si>
-    <t>Familienanamnese.FamilienmitgliedVerstorben</t>
+    <t>familienanamnese.familienmitgliedVerstorben</t>
   </si>
   <si>
     <t>FamilyMemberHistory.deceased[x]:deceasedDate</t>
@@ -1067,7 +1067,7 @@
     <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
-    <t>Familienanamnese.AndereSE</t>
+    <t>familienanamnese.andereSE</t>
   </si>
   <si>
     <t>FamilyMemberHistory.reasonCode.id</t>
@@ -1362,7 +1362,7 @@
     <t>Angabe zur Penetranz der genetischen Variante bei der Erkrankung des Familienmitglieds</t>
   </si>
   <si>
-    <t>Familienanamnese.Penetranz</t>
+    <t>familienanamnese.penetranz</t>
   </si>
   <si>
     <t>FamilyMemberHistory.condition.modifierExtension</t>
@@ -1658,7 +1658,7 @@
     <t>Gibt an, ob diese Erkrankung zum Tod des Familienmitglieds beigetragen hat. Relevant für die Dokumentation von Todesfällen durch seltene Erkrankungen in der Familie.</t>
   </si>
   <si>
-    <t>Familienanamnese.TodDurchSE</t>
+    <t>familienanamnese.TodDurchSE</t>
   </si>
   <si>
     <t>FamilyMemberHistory.condition.onset[x]</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4883" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4883" uniqueCount="538">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -603,6 +603,9 @@
 ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
+    <t>persoenlicheInfosIndexpatient</t>
+  </si>
+  <si>
     <t>FamilyMemberHistory.date</t>
   </si>
   <si>
@@ -622,7 +625,7 @@
     <t>Allows determination of how current the summary is.</t>
   </si>
   <si>
-    <t>Dokumentationsdatum</t>
+    <t>familienanamnese.dokumentationsdatum</t>
   </si>
   <si>
     <t>FamilyMemberHistory.name</t>
@@ -1658,7 +1661,7 @@
     <t>Gibt an, ob diese Erkrankung zum Tod des Familienmitglieds beigetragen hat. Relevant für die Dokumentation von Todesfällen durch seltene Erkrankungen in der Familie.</t>
   </si>
   <si>
-    <t>familienanamnese.TodDurchSE</t>
+    <t>familienanamnese.todDurchSE</t>
   </si>
   <si>
     <t>FamilyMemberHistory.condition.onset[x]</t>
@@ -3889,7 +3892,7 @@
         <v>186</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>75</v>
@@ -3897,10 +3900,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3923,19 +3926,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3984,7 +3987,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3999,7 +4002,7 @@
         <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>75</v>
@@ -4007,10 +4010,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4033,19 +4036,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -4094,7 +4097,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4117,10 +4120,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4146,10 +4149,10 @@
         <v>172</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>175</v>
@@ -4181,10 +4184,10 @@
         <v>177</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>75</v>
@@ -4202,7 +4205,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>85</v>
@@ -4217,7 +4220,7 @@
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
@@ -4225,10 +4228,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4251,13 +4254,13 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4308,7 +4311,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4331,10 +4334,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4360,10 +4363,10 @@
         <v>129</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>147</v>
@@ -4416,7 +4419,7 @@
         <v>134</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4439,10 +4442,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4465,19 +4468,19 @@
         <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -4514,7 +4517,7 @@
         <v>75</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4524,7 +4527,7 @@
         <v>134</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4547,13 +4550,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -4575,19 +4578,19 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>75</v>
@@ -4597,7 +4600,7 @@
         <v>75</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>75</v>
@@ -4612,11 +4615,11 @@
         <v>75</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>75</v>
@@ -4634,7 +4637,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4657,10 +4660,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4683,13 +4686,13 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4740,7 +4743,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4763,10 +4766,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4792,10 +4795,10 @@
         <v>129</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>147</v>
@@ -4848,7 +4851,7 @@
         <v>134</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4871,13 +4874,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="B27" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="C27" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>144</v>
@@ -4899,13 +4902,13 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="M27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>147</v>
@@ -4958,7 +4961,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4981,13 +4984,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>144</v>
@@ -5009,13 +5012,13 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>147</v>
@@ -5068,7 +5071,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -5091,13 +5094,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>144</v>
@@ -5119,13 +5122,13 @@
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>147</v>
@@ -5178,7 +5181,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5201,10 +5204,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5230,16 +5233,16 @@
         <v>100</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -5288,7 +5291,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5311,10 +5314,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5337,16 +5340,16 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5396,7 +5399,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5419,10 +5422,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5448,16 +5451,16 @@
         <v>106</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>75</v>
@@ -5506,7 +5509,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5529,10 +5532,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5555,19 +5558,19 @@
         <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -5616,7 +5619,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5639,10 +5642,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5665,19 +5668,19 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5726,7 +5729,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5749,13 +5752,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>75</v>
@@ -5777,19 +5780,19 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5799,7 +5802,7 @@
         <v>75</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>75</v>
@@ -5814,11 +5817,11 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5836,7 +5839,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5859,10 +5862,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5885,19 +5888,19 @@
         <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5946,7 +5949,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5969,10 +5972,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5998,16 +6001,16 @@
         <v>172</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -6032,13 +6035,13 @@
         <v>75</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>75</v>
@@ -6056,7 +6059,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6071,7 +6074,7 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
@@ -6079,10 +6082,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6105,17 +6108,17 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -6164,7 +6167,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -6173,7 +6176,7 @@
         <v>85</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>98</v>
@@ -6187,10 +6190,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6213,19 +6216,19 @@
         <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -6274,16 +6277,16 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI39" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>98</v>
@@ -6297,10 +6300,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6323,71 +6326,71 @@
         <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q40" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="R40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="P40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q40" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="R40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>308</v>
-      </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
@@ -6395,7 +6398,7 @@
         <v>85</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>98</v>
@@ -6409,10 +6412,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6435,13 +6438,13 @@
         <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6480,7 +6483,7 @@
         <v>75</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -6490,7 +6493,7 @@
         <v>134</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6513,13 +6516,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>75</v>
@@ -6541,13 +6544,13 @@
         <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6598,7 +6601,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6613,7 +6616,7 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>75</v>
@@ -6621,13 +6624,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>75</v>
@@ -6649,13 +6652,13 @@
         <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6706,7 +6709,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6721,7 +6724,7 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6729,13 +6732,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>75</v>
@@ -6757,13 +6760,13 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6814,7 +6817,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6829,7 +6832,7 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6837,10 +6840,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6866,13 +6869,13 @@
         <v>172</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6901,10 +6904,10 @@
         <v>177</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>75</v>
@@ -6922,7 +6925,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6937,7 +6940,7 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6945,10 +6948,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6971,13 +6974,13 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7028,7 +7031,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7051,10 +7054,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7080,10 +7083,10 @@
         <v>129</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>147</v>
@@ -7136,7 +7139,7 @@
         <v>134</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7159,10 +7162,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7185,19 +7188,19 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -7234,7 +7237,7 @@
         <v>75</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
@@ -7244,7 +7247,7 @@
         <v>134</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7267,13 +7270,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>75</v>
@@ -7295,19 +7298,19 @@
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -7317,7 +7320,7 @@
         <v>75</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>75</v>
@@ -7336,7 +7339,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>75</v>
@@ -7354,7 +7357,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7377,10 +7380,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7403,13 +7406,13 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7460,7 +7463,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7483,10 +7486,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7512,10 +7515,10 @@
         <v>129</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>147</v>
@@ -7568,7 +7571,7 @@
         <v>134</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7591,10 +7594,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7620,16 +7623,16 @@
         <v>100</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7678,7 +7681,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7701,10 +7704,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7727,16 +7730,16 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>4</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7786,7 +7789,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7809,10 +7812,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7841,13 +7844,13 @@
         <v>63</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -7896,7 +7899,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7919,10 +7922,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7945,19 +7948,19 @@
         <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -8006,7 +8009,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8029,10 +8032,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8055,19 +8058,19 @@
         <v>86</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -8116,7 +8119,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8139,13 +8142,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>75</v>
@@ -8167,19 +8170,19 @@
         <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -8189,7 +8192,7 @@
         <v>75</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>75</v>
@@ -8208,7 +8211,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>75</v>
@@ -8226,7 +8229,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8249,10 +8252,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8275,13 +8278,13 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8332,7 +8335,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8355,10 +8358,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8384,10 +8387,10 @@
         <v>129</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>147</v>
@@ -8440,7 +8443,7 @@
         <v>134</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8463,10 +8466,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8492,16 +8495,16 @@
         <v>100</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -8550,7 +8553,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8573,10 +8576,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8599,16 +8602,16 @@
         <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8658,7 +8661,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8681,10 +8684,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8713,13 +8716,13 @@
         <v>63</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>75</v>
@@ -8768,7 +8771,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8791,10 +8794,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8817,19 +8820,19 @@
         <v>86</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>75</v>
@@ -8878,7 +8881,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8901,10 +8904,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8927,19 +8930,19 @@
         <v>86</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -8988,7 +8991,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9011,13 +9014,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>75</v>
@@ -9039,19 +9042,19 @@
         <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>75</v>
@@ -9061,7 +9064,7 @@
         <v>75</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>75</v>
@@ -9080,7 +9083,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>75</v>
@@ -9098,7 +9101,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9121,10 +9124,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9147,13 +9150,13 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9204,7 +9207,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -9227,10 +9230,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9256,10 +9259,10 @@
         <v>129</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>147</v>
@@ -9312,7 +9315,7 @@
         <v>134</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9335,10 +9338,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9364,16 +9367,16 @@
         <v>100</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -9422,7 +9425,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9445,10 +9448,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9471,16 +9474,16 @@
         <v>86</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9530,7 +9533,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9553,10 +9556,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9585,13 +9588,13 @@
         <v>63</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9640,7 +9643,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9663,10 +9666,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9689,19 +9692,19 @@
         <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -9750,7 +9753,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9773,10 +9776,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9799,19 +9802,19 @@
         <v>86</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -9860,7 +9863,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -9883,13 +9886,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>75</v>
@@ -9911,19 +9914,19 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -9933,7 +9936,7 @@
         <v>75</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>75</v>
@@ -9952,7 +9955,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -9970,7 +9973,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -9993,10 +9996,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10019,13 +10022,13 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10076,7 +10079,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10099,10 +10102,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10128,10 +10131,10 @@
         <v>129</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>147</v>
@@ -10184,7 +10187,7 @@
         <v>134</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10207,10 +10210,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10236,16 +10239,16 @@
         <v>100</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>75</v>
@@ -10294,7 +10297,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10317,10 +10320,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10343,16 +10346,16 @@
         <v>86</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10402,7 +10405,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10425,10 +10428,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10457,13 +10460,13 @@
         <v>63</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>75</v>
@@ -10512,7 +10515,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10535,10 +10538,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10561,19 +10564,19 @@
         <v>86</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>75</v>
@@ -10622,7 +10625,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10645,10 +10648,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10671,19 +10674,19 @@
         <v>86</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>75</v>
@@ -10732,7 +10735,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -10755,10 +10758,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10781,19 +10784,19 @@
         <v>86</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -10842,7 +10845,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -10865,10 +10868,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10891,13 +10894,13 @@
         <v>86</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>185</v>
@@ -10950,7 +10953,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -10973,10 +10976,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10999,16 +11002,16 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11058,7 +11061,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11081,10 +11084,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11107,13 +11110,13 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11164,7 +11167,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -11187,10 +11190,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11213,13 +11216,13 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11270,7 +11273,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11293,10 +11296,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11322,10 +11325,10 @@
         <v>129</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>147</v>
@@ -11378,7 +11381,7 @@
         <v>134</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -11401,13 +11404,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="B87" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="C87" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>75</v>
@@ -11429,13 +11432,13 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11486,7 +11489,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -11501,7 +11504,7 @@
         <v>136</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>75</v>
@@ -11509,14 +11512,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -11538,10 +11541,10 @@
         <v>129</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>147</v>
@@ -11596,7 +11599,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -11619,10 +11622,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11648,10 +11651,10 @@
         <v>172</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>175</v>
@@ -11683,10 +11686,10 @@
         <v>177</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>75</v>
@@ -11704,7 +11707,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>85</v>
@@ -11727,10 +11730,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11753,13 +11756,13 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -11810,7 +11813,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -11833,10 +11836,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11862,10 +11865,10 @@
         <v>129</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>147</v>
@@ -11918,7 +11921,7 @@
         <v>134</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -11941,10 +11944,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11967,19 +11970,19 @@
         <v>86</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>75</v>
@@ -12016,7 +12019,7 @@
         <v>75</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC92" s="2"/>
       <c r="AD92" t="s" s="2">
@@ -12026,7 +12029,7 @@
         <v>134</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12049,13 +12052,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>75</v>
@@ -12077,19 +12080,19 @@
         <v>86</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>75</v>
@@ -12099,7 +12102,7 @@
         <v>75</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>75</v>
@@ -12118,7 +12121,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>75</v>
@@ -12136,7 +12139,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12151,7 +12154,7 @@
         <v>98</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>75</v>
@@ -12159,10 +12162,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12185,13 +12188,13 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12242,7 +12245,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12265,10 +12268,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12294,10 +12297,10 @@
         <v>129</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>147</v>
@@ -12350,7 +12353,7 @@
         <v>134</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -12373,13 +12376,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="B96" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="C96" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>144</v>
@@ -12401,13 +12404,13 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>147</v>
@@ -12460,7 +12463,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -12483,13 +12486,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>144</v>
@@ -12511,13 +12514,13 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>147</v>
@@ -12570,7 +12573,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -12593,13 +12596,13 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>144</v>
@@ -12621,13 +12624,13 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>147</v>
@@ -12680,7 +12683,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -12703,10 +12706,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12732,23 +12735,23 @@
         <v>100</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>75</v>
@@ -12790,7 +12793,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -12813,10 +12816,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12839,16 +12842,16 @@
         <v>86</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>4</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12898,7 +12901,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -12921,10 +12924,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12953,13 +12956,13 @@
         <v>63</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>75</v>
@@ -12972,7 +12975,7 @@
         <v>75</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>75</v>
@@ -13008,7 +13011,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -13020,7 +13023,7 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>75</v>
@@ -13031,10 +13034,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13057,19 +13060,19 @@
         <v>86</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>75</v>
@@ -13118,7 +13121,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -13141,10 +13144,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13167,19 +13170,19 @@
         <v>86</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>75</v>
@@ -13228,7 +13231,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -13251,13 +13254,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>75</v>
@@ -13279,19 +13282,19 @@
         <v>86</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>75</v>
@@ -13301,7 +13304,7 @@
         <v>75</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>75</v>
@@ -13320,7 +13323,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>75</v>
@@ -13338,7 +13341,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -13361,10 +13364,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13387,13 +13390,13 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13444,7 +13447,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -13467,10 +13470,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13496,10 +13499,10 @@
         <v>129</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>147</v>
@@ -13552,7 +13555,7 @@
         <v>134</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -13575,10 +13578,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13604,23 +13607,23 @@
         <v>100</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>75</v>
@@ -13662,7 +13665,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -13685,10 +13688,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13711,16 +13714,16 @@
         <v>86</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -13770,7 +13773,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -13793,10 +13796,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13825,13 +13828,13 @@
         <v>63</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>75</v>
@@ -13880,7 +13883,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -13903,10 +13906,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13929,19 +13932,19 @@
         <v>86</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>75</v>
@@ -13990,7 +13993,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -14013,10 +14016,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14039,19 +14042,19 @@
         <v>86</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>75</v>
@@ -14100,7 +14103,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14123,13 +14126,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>75</v>
@@ -14151,19 +14154,19 @@
         <v>86</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>75</v>
@@ -14173,7 +14176,7 @@
         <v>75</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>75</v>
@@ -14192,7 +14195,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>75</v>
@@ -14210,7 +14213,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -14225,7 +14228,7 @@
         <v>98</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>75</v>
@@ -14233,10 +14236,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14259,13 +14262,13 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14316,7 +14319,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -14339,10 +14342,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14368,10 +14371,10 @@
         <v>129</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>147</v>
@@ -14424,7 +14427,7 @@
         <v>134</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -14447,10 +14450,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14476,16 +14479,16 @@
         <v>100</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>75</v>
@@ -14534,7 +14537,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -14557,10 +14560,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14583,16 +14586,16 @@
         <v>86</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -14642,7 +14645,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -14665,10 +14668,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14697,13 +14700,13 @@
         <v>63</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>75</v>
@@ -14752,7 +14755,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -14775,10 +14778,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14801,19 +14804,19 @@
         <v>86</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -14862,7 +14865,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -14885,10 +14888,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14911,19 +14914,19 @@
         <v>86</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>75</v>
@@ -14972,7 +14975,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -14995,13 +14998,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>75</v>
@@ -15023,19 +15026,19 @@
         <v>86</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>75</v>
@@ -15045,7 +15048,7 @@
         <v>75</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>75</v>
@@ -15064,7 +15067,7 @@
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>75</v>
@@ -15082,7 +15085,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -15097,7 +15100,7 @@
         <v>98</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>75</v>
@@ -15105,10 +15108,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15131,13 +15134,13 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15188,7 +15191,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -15211,10 +15214,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15240,10 +15243,10 @@
         <v>129</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>147</v>
@@ -15296,7 +15299,7 @@
         <v>134</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -15319,10 +15322,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15348,16 +15351,16 @@
         <v>100</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>75</v>
@@ -15406,7 +15409,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -15429,10 +15432,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15455,16 +15458,16 @@
         <v>86</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -15514,7 +15517,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -15537,10 +15540,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15569,13 +15572,13 @@
         <v>63</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>75</v>
@@ -15624,7 +15627,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -15647,10 +15650,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15673,19 +15676,19 @@
         <v>86</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>75</v>
@@ -15734,7 +15737,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -15757,10 +15760,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15783,19 +15786,19 @@
         <v>86</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>75</v>
@@ -15844,7 +15847,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
@@ -15867,13 +15870,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>75</v>
@@ -15895,19 +15898,19 @@
         <v>86</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>75</v>
@@ -15917,7 +15920,7 @@
         <v>75</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>75</v>
@@ -15956,7 +15959,7 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -15979,10 +15982,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16005,13 +16008,13 @@
         <v>75</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -16062,7 +16065,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -16085,10 +16088,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16114,10 +16117,10 @@
         <v>129</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>147</v>
@@ -16170,7 +16173,7 @@
         <v>134</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -16193,10 +16196,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16222,16 +16225,16 @@
         <v>100</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>75</v>
@@ -16280,7 +16283,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -16303,10 +16306,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16329,16 +16332,16 @@
         <v>86</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -16388,7 +16391,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -16411,10 +16414,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16440,14 +16443,14 @@
         <v>106</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>75</v>
@@ -16496,7 +16499,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -16519,10 +16522,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16545,17 +16548,17 @@
         <v>86</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>75</v>
@@ -16604,7 +16607,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -16627,10 +16630,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16653,19 +16656,19 @@
         <v>86</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>75</v>
@@ -16714,7 +16717,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -16737,10 +16740,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16763,19 +16766,19 @@
         <v>86</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>75</v>
@@ -16824,7 +16827,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -16847,10 +16850,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16876,10 +16879,10 @@
         <v>172</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>175</v>
@@ -16911,10 +16914,10 @@
         <v>177</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>75</v>
@@ -16932,7 +16935,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -16955,10 +16958,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16981,13 +16984,13 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -17038,7 +17041,7 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -17053,7 +17056,7 @@
         <v>98</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>75</v>
@@ -17061,10 +17064,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17087,17 +17090,17 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>75</v>
@@ -17134,7 +17137,7 @@
         <v>75</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AC139" s="2"/>
       <c r="AD139" t="s" s="2">
@@ -17144,7 +17147,7 @@
         <v>134</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -17167,13 +17170,13 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>75</v>
@@ -17195,17 +17198,17 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>75</v>
@@ -17254,7 +17257,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -17269,7 +17272,7 @@
         <v>98</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>75</v>
@@ -17277,10 +17280,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17303,16 +17306,16 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -17362,7 +17365,7 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -450,7 +450,7 @@
     <t>vonSEBetroffen</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/StructureDefinition/von-seltene-betroffen}
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/StructureDefinition/mii-ex-von-se-betroffen}
 </t>
   </si>
   <si>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -450,7 +450,7 @@
     <t>vonSEBetroffen</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/StructureDefinition/mii-ex-von-se-betroffen}
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/StructureDefinition/mii-ex-seltene-von-se-betroffen}
 </t>
   </si>
   <si>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-familienanamnese.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
